--- a/code/data/combined/cmb+pelg+jmul-lcdm-free.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-lcdm-free.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39309903.71068951</v>
+        <v>44521433.80775819</v>
       </c>
       <c r="C2" t="n">
-        <v>-134472624.57561</v>
+        <v>-148871301.4614232</v>
       </c>
       <c r="D2" t="n">
-        <v>40498344.88891232</v>
+        <v>46542703.77667018</v>
       </c>
       <c r="E2" t="n">
-        <v>-328826.7714413111</v>
+        <v>-386670.9606859339</v>
       </c>
       <c r="F2" t="n">
-        <v>-1339492.473711304</v>
+        <v>-1342250.050937704</v>
       </c>
       <c r="G2" t="n">
-        <v>879085.3645681102</v>
+        <v>1047468.985388712</v>
       </c>
       <c r="H2" t="n">
-        <v>-2582307.6068324</v>
+        <v>-2937963.25843927</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134472624.575653</v>
+        <v>-148871301.4613353</v>
       </c>
       <c r="C3" t="n">
-        <v>887787810.5292406</v>
+        <v>895579660.6708298</v>
       </c>
       <c r="D3" t="n">
-        <v>-89236526.53149243</v>
+        <v>-111670939.5483021</v>
       </c>
       <c r="E3" t="n">
-        <v>15622280.82640174</v>
+        <v>16225352.75581323</v>
       </c>
       <c r="F3" t="n">
-        <v>6725763.597954061</v>
+        <v>6678773.488553813</v>
       </c>
       <c r="G3" t="n">
-        <v>-3830849.072266923</v>
+        <v>-4434906.740830824</v>
       </c>
       <c r="H3" t="n">
-        <v>7955227.511495453</v>
+        <v>8983941.631675022</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40498344.88890784</v>
+        <v>46542703.77668043</v>
       </c>
       <c r="C4" t="n">
-        <v>-89236526.53143121</v>
+        <v>-111670939.54843</v>
       </c>
       <c r="D4" t="n">
-        <v>48990351.07576764</v>
+        <v>55092578.16113847</v>
       </c>
       <c r="E4" t="n">
-        <v>921795.3901474421</v>
+        <v>834589.4580857229</v>
       </c>
       <c r="F4" t="n">
-        <v>-954046.0478058696</v>
+        <v>-978168.1870837978</v>
       </c>
       <c r="G4" t="n">
-        <v>971974.4851704772</v>
+        <v>1153342.968898802</v>
       </c>
       <c r="H4" t="n">
-        <v>-2835900.032191387</v>
+        <v>-3237876.53481444</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-328826.7714428463</v>
+        <v>-386670.9606825283</v>
       </c>
       <c r="C5" t="n">
-        <v>15622280.82640626</v>
+        <v>16225352.75580375</v>
       </c>
       <c r="D5" t="n">
-        <v>921795.3901455512</v>
+        <v>834589.458089334</v>
       </c>
       <c r="E5" t="n">
-        <v>1030767.846398891</v>
+        <v>1117992.601100488</v>
       </c>
       <c r="F5" t="n">
-        <v>29917.84075138746</v>
+        <v>48796.32697415931</v>
       </c>
       <c r="G5" t="n">
-        <v>-77271.80251381379</v>
+        <v>-84827.69389391407</v>
       </c>
       <c r="H5" t="n">
-        <v>-6239.26166838479</v>
+        <v>-5472.509808322719</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1339492.473711377</v>
+        <v>-1342250.05093751</v>
       </c>
       <c r="C6" t="n">
-        <v>6725763.597952889</v>
+        <v>6678773.488555882</v>
       </c>
       <c r="D6" t="n">
-        <v>-954046.0478059853</v>
+        <v>-978168.1870833607</v>
       </c>
       <c r="E6" t="n">
-        <v>29917.84075134353</v>
+        <v>48796.32697423756</v>
       </c>
       <c r="F6" t="n">
-        <v>637642.8265049806</v>
+        <v>638620.3949297542</v>
       </c>
       <c r="G6" t="n">
-        <v>103899.4427337138</v>
+        <v>102682.2695589077</v>
       </c>
       <c r="H6" t="n">
-        <v>42096.58699851023</v>
+        <v>41197.21617643569</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>879085.3645682601</v>
+        <v>1047468.985388445</v>
       </c>
       <c r="C7" t="n">
-        <v>-3830849.072266368</v>
+        <v>-4434906.740832165</v>
       </c>
       <c r="D7" t="n">
-        <v>971974.48517077</v>
+        <v>1153342.968898279</v>
       </c>
       <c r="E7" t="n">
-        <v>-77271.8025137706</v>
+        <v>-84827.69389399105</v>
       </c>
       <c r="F7" t="n">
-        <v>103899.4427337071</v>
+        <v>102682.2695589043</v>
       </c>
       <c r="G7" t="n">
-        <v>66769.24939534687</v>
+        <v>72669.37597598703</v>
       </c>
       <c r="H7" t="n">
-        <v>-71180.87005632964</v>
+        <v>-82394.73390680994</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2582307.606832331</v>
+        <v>-2937963.258439461</v>
       </c>
       <c r="C8" t="n">
-        <v>7955227.511492336</v>
+        <v>8983941.631681541</v>
       </c>
       <c r="D8" t="n">
-        <v>-2835900.032191624</v>
+        <v>-3237876.534813961</v>
       </c>
       <c r="E8" t="n">
-        <v>-6239.261668494494</v>
+        <v>-5472.509808099185</v>
       </c>
       <c r="F8" t="n">
-        <v>42096.58699850607</v>
+        <v>41197.21617644757</v>
       </c>
       <c r="G8" t="n">
-        <v>-71180.87005631746</v>
+        <v>-82394.73390683207</v>
       </c>
       <c r="H8" t="n">
-        <v>178514.0622420082</v>
+        <v>202848.6948056764</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+pelg+jmul-lcdm-free.xlsx
+++ b/code/data/combined/cmb+pelg+jmul-lcdm-free.xlsx
@@ -472,25 +472,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44521433.80775819</v>
+        <v>43671284.56693956</v>
       </c>
       <c r="C2" t="n">
-        <v>-148871301.4614232</v>
+        <v>-146032037.9519669</v>
       </c>
       <c r="D2" t="n">
-        <v>46542703.77667018</v>
+        <v>45623756.26113153</v>
       </c>
       <c r="E2" t="n">
-        <v>-386670.9606859339</v>
+        <v>-379416.1539007421</v>
       </c>
       <c r="F2" t="n">
-        <v>-1342250.050937704</v>
+        <v>-1334633.657279689</v>
       </c>
       <c r="G2" t="n">
-        <v>1047468.985388712</v>
+        <v>1020578.406346655</v>
       </c>
       <c r="H2" t="n">
-        <v>-2937963.25843927</v>
+        <v>-2878123.168839374</v>
       </c>
     </row>
     <row r="3">
@@ -500,25 +500,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148871301.4613353</v>
+        <v>-146032037.9519296</v>
       </c>
       <c r="C3" t="n">
-        <v>895579660.6708298</v>
+        <v>876730590.5469518</v>
       </c>
       <c r="D3" t="n">
-        <v>-111670939.5483021</v>
+        <v>-109841979.6000199</v>
       </c>
       <c r="E3" t="n">
-        <v>16225352.75581323</v>
+        <v>15993899.89060177</v>
       </c>
       <c r="F3" t="n">
-        <v>6678773.488553813</v>
+        <v>6606462.467111537</v>
       </c>
       <c r="G3" t="n">
-        <v>-4434906.740830824</v>
+        <v>-4341449.679966884</v>
       </c>
       <c r="H3" t="n">
-        <v>8983941.631675022</v>
+        <v>8805594.644194394</v>
       </c>
     </row>
     <row r="4">
@@ -528,25 +528,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46542703.77668043</v>
+        <v>45623756.26113567</v>
       </c>
       <c r="C4" t="n">
-        <v>-111670939.54843</v>
+        <v>-109841979.6000738</v>
       </c>
       <c r="D4" t="n">
-        <v>55092578.16113847</v>
+        <v>53932634.04738718</v>
       </c>
       <c r="E4" t="n">
-        <v>834589.4580857229</v>
+        <v>816073.8811666473</v>
       </c>
       <c r="F4" t="n">
-        <v>-978168.1870837978</v>
+        <v>-974232.5062271736</v>
       </c>
       <c r="G4" t="n">
-        <v>1153342.968898802</v>
+        <v>1124804.266928159</v>
       </c>
       <c r="H4" t="n">
-        <v>-3237876.53481444</v>
+        <v>-3170427.902424754</v>
       </c>
     </row>
     <row r="5">
@@ -556,25 +556,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-386670.9606825283</v>
+        <v>-379416.153898982</v>
       </c>
       <c r="C5" t="n">
-        <v>16225352.75580375</v>
+        <v>15993899.89059691</v>
       </c>
       <c r="D5" t="n">
-        <v>834589.458089334</v>
+        <v>816073.8811684193</v>
       </c>
       <c r="E5" t="n">
-        <v>1117992.601100488</v>
+        <v>1110110.42256629</v>
       </c>
       <c r="F5" t="n">
-        <v>48796.32697415931</v>
+        <v>48716.74950029791</v>
       </c>
       <c r="G5" t="n">
-        <v>-84827.69389391407</v>
+        <v>-84279.01038145159</v>
       </c>
       <c r="H5" t="n">
-        <v>-5472.509808322719</v>
+        <v>-5348.626876044716</v>
       </c>
     </row>
     <row r="6">
@@ -584,25 +584,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1342250.05093751</v>
+        <v>-1334633.657279648</v>
       </c>
       <c r="C6" t="n">
-        <v>6678773.488555882</v>
+        <v>6606462.467111732</v>
       </c>
       <c r="D6" t="n">
-        <v>-978168.1870833607</v>
+        <v>-974232.5062271629</v>
       </c>
       <c r="E6" t="n">
-        <v>48796.32697423756</v>
+        <v>48716.7495003002</v>
       </c>
       <c r="F6" t="n">
-        <v>638620.3949297542</v>
+        <v>634464.5000966155</v>
       </c>
       <c r="G6" t="n">
-        <v>102682.2695589077</v>
+        <v>102551.139183311</v>
       </c>
       <c r="H6" t="n">
-        <v>41197.21617643569</v>
+        <v>40814.74905559606</v>
       </c>
     </row>
     <row r="7">
@@ -612,25 +612,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1047468.985388445</v>
+        <v>1020578.406346488</v>
       </c>
       <c r="C7" t="n">
-        <v>-4434906.740832165</v>
+        <v>-4341449.679967548</v>
       </c>
       <c r="D7" t="n">
-        <v>1153342.968898279</v>
+        <v>1124804.26692787</v>
       </c>
       <c r="E7" t="n">
-        <v>-84827.69389399105</v>
+        <v>-84279.01038149872</v>
       </c>
       <c r="F7" t="n">
-        <v>102682.2695589043</v>
+        <v>102551.1391833049</v>
       </c>
       <c r="G7" t="n">
-        <v>72669.37597598703</v>
+        <v>71761.94659695895</v>
       </c>
       <c r="H7" t="n">
-        <v>-82394.73390680994</v>
+        <v>-80510.04120535695</v>
       </c>
     </row>
     <row r="8">
@@ -640,25 +640,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-2937963.258439461</v>
+        <v>-2878123.168839453</v>
       </c>
       <c r="C8" t="n">
-        <v>8983941.631681541</v>
+        <v>8805594.644197235</v>
       </c>
       <c r="D8" t="n">
-        <v>-3237876.534813961</v>
+        <v>-3170427.902424552</v>
       </c>
       <c r="E8" t="n">
-        <v>-5472.509808099185</v>
+        <v>-5348.626875929878</v>
       </c>
       <c r="F8" t="n">
-        <v>41197.21617644757</v>
+        <v>40814.74905559507</v>
       </c>
       <c r="G8" t="n">
-        <v>-82394.73390683207</v>
+        <v>-80510.04120537019</v>
       </c>
       <c r="H8" t="n">
-        <v>202848.6948056764</v>
+        <v>198571.6201140827</v>
       </c>
     </row>
   </sheetData>
